--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,6 +907,2251 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123235689</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>441596</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7028775</v>
+      </c>
+      <c r="S4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>123233043</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>441571</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7028720</v>
+      </c>
+      <c r="S5" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123233946</v>
+      </c>
+      <c r="B6" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>441609</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7028716</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123235737</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>441617</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7028768</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123236259</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>441633</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7028804</v>
+      </c>
+      <c r="S8" t="n">
+        <v>8</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123234048</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>441630</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7028692</v>
+      </c>
+      <c r="S9" t="n">
+        <v>9</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>123235901</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>441683</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7028765</v>
+      </c>
+      <c r="S10" t="n">
+        <v>11</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123236631</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hästmon, Hästmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>441559</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7028811</v>
+      </c>
+      <c r="S11" t="n">
+        <v>9</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>123233568</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57631</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>441564</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7028721</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123234752</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>441583</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7028658</v>
+      </c>
+      <c r="S13" t="n">
+        <v>9</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På en gammal gran intill ett fuktstråk.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123236127</v>
+      </c>
+      <c r="B14" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>441667</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7028798</v>
+      </c>
+      <c r="S14" t="n">
+        <v>8</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123235031</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>441542</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7028672</v>
+      </c>
+      <c r="S15" t="n">
+        <v>8</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123235545</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97325</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>441587</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7028776</v>
+      </c>
+      <c r="S16" t="n">
+        <v>7</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123236343</v>
+      </c>
+      <c r="B17" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Hästmon, Hästmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>441640</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7028845</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123233597</v>
+      </c>
+      <c r="B18" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>441569</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7028701</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123234252</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>441667</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7028689</v>
+      </c>
+      <c r="S19" t="n">
+        <v>8</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123233772</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Raskhus, Raskhus, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>441598</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7028738</v>
+      </c>
+      <c r="S20" t="n">
+        <v>8</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123236460</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Hästmon, Hästmon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>441626</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7028860</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123235689</v>
+        <v>123235901</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441596</v>
+        <v>441683</v>
       </c>
       <c r="R4" t="n">
-        <v>7028775</v>
+        <v>7028765</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,6 +985,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123233043</v>
+        <v>123236127</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1076,10 +1081,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441571</v>
+        <v>441667</v>
       </c>
       <c r="R5" t="n">
-        <v>7028720</v>
+        <v>7028798</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1112,6 +1117,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1163,7 +1173,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123233946</v>
+        <v>123235737</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1203,13 +1213,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441609</v>
+        <v>441617</v>
       </c>
       <c r="R6" t="n">
-        <v>7028716</v>
+        <v>7028768</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1239,11 +1249,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1295,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123235737</v>
+        <v>123235545</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>97325</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1307,41 +1312,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441617</v>
+        <v>441587</v>
       </c>
       <c r="R7" t="n">
-        <v>7028768</v>
+        <v>7028776</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1385,26 +1395,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1422,10 +1412,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123236259</v>
+        <v>123233568</v>
       </c>
       <c r="B8" t="n">
-        <v>97319</v>
+        <v>57631</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,31 +1424,40 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1467,13 +1466,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441633</v>
+        <v>441564</v>
       </c>
       <c r="R8" t="n">
-        <v>7028804</v>
+        <v>7028721</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,6 +1504,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1513,6 +1517,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1529,7 +1538,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123234048</v>
+        <v>123234752</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1569,10 +1578,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441630</v>
+        <v>441583</v>
       </c>
       <c r="R9" t="n">
-        <v>7028692</v>
+        <v>7028658</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1609,7 +1618,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,10 +1670,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123235901</v>
+        <v>123236259</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,41 +1682,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441683</v>
+        <v>441633</v>
       </c>
       <c r="R10" t="n">
-        <v>7028765</v>
+        <v>7028804</v>
       </c>
       <c r="S10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,11 +1753,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1752,31 +1761,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1793,7 +1777,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123236631</v>
+        <v>123233597</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1829,14 +1813,14 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441559</v>
+        <v>441569</v>
       </c>
       <c r="R11" t="n">
-        <v>7028811</v>
+        <v>7028701</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1882,7 +1866,7 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -1920,10 +1904,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123233568</v>
+        <v>123233043</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1936,51 +1920,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441564</v>
+        <v>441571</v>
       </c>
       <c r="R12" t="n">
-        <v>7028721</v>
+        <v>7028720</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,11 +1982,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2029,6 +1994,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2046,10 +2031,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123234752</v>
+        <v>123234252</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2058,25 +2043,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2086,13 +2071,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441583</v>
+        <v>441667</v>
       </c>
       <c r="R13" t="n">
-        <v>7028658</v>
+        <v>7028689</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2124,11 +2109,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2137,31 +2117,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2178,10 +2133,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123236127</v>
+        <v>123236460</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2190,41 +2145,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441667</v>
+        <v>441626</v>
       </c>
       <c r="R14" t="n">
-        <v>7028798</v>
+        <v>7028860</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2256,11 +2216,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2269,31 +2224,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2310,7 +2240,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123235031</v>
+        <v>123236343</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2346,14 +2276,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441542</v>
+        <v>441640</v>
       </c>
       <c r="R15" t="n">
-        <v>7028672</v>
+        <v>7028845</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2388,11 +2318,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2419,12 +2344,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2442,10 +2367,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123235545</v>
+        <v>123234048</v>
       </c>
       <c r="B16" t="n">
-        <v>97325</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2454,46 +2379,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441587</v>
+        <v>441630</v>
       </c>
       <c r="R16" t="n">
-        <v>7028776</v>
+        <v>7028692</v>
       </c>
       <c r="S16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2525,6 +2445,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2537,6 +2462,26 @@
       <c r="AH16" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2554,7 +2499,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236343</v>
+        <v>123235031</v>
       </c>
       <c r="B17" t="n">
         <v>78766</v>
@@ -2590,14 +2535,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441640</v>
+        <v>441542</v>
       </c>
       <c r="R17" t="n">
-        <v>7028845</v>
+        <v>7028672</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2632,6 +2577,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2658,12 +2608,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2681,7 +2631,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123233597</v>
+        <v>123233946</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2721,13 +2671,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441569</v>
+        <v>441609</v>
       </c>
       <c r="R18" t="n">
-        <v>7028701</v>
+        <v>7028716</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2757,6 +2707,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2808,10 +2763,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123234252</v>
+        <v>123236631</v>
       </c>
       <c r="B19" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2820,41 +2775,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441667</v>
+        <v>441559</v>
       </c>
       <c r="R19" t="n">
-        <v>7028689</v>
+        <v>7028811</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2894,6 +2849,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2910,7 +2890,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123233772</v>
+        <v>123235689</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2944,21 +2924,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441598</v>
+        <v>441596</v>
       </c>
       <c r="R20" t="n">
-        <v>7028738</v>
+        <v>7028775</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -2991,11 +2966,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3047,10 +3017,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123236460</v>
+        <v>123233772</v>
       </c>
       <c r="B21" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3059,46 +3029,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441626</v>
+        <v>441598</v>
       </c>
       <c r="R21" t="n">
-        <v>7028860</v>
+        <v>7028738</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3130,6 +3100,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3138,6 +3113,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123235901</v>
+        <v>123233568</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +925,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441683</v>
+        <v>441564</v>
       </c>
       <c r="R4" t="n">
-        <v>7028765</v>
+        <v>7028721</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gammal gran.</t>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,26 +1018,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,7 +1035,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236127</v>
+        <v>123233043</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1081,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441667</v>
+        <v>441571</v>
       </c>
       <c r="R5" t="n">
-        <v>7028798</v>
+        <v>7028720</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1117,11 +1111,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1173,7 +1162,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123235737</v>
+        <v>123235689</v>
       </c>
       <c r="B6" t="n">
         <v>78766</v>
@@ -1213,13 +1202,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441617</v>
+        <v>441596</v>
       </c>
       <c r="R6" t="n">
-        <v>7028768</v>
+        <v>7028775</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1300,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123235545</v>
+        <v>123235737</v>
       </c>
       <c r="B7" t="n">
-        <v>97325</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1312,46 +1301,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441587</v>
+        <v>441617</v>
       </c>
       <c r="R7" t="n">
-        <v>7028776</v>
+        <v>7028768</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1395,6 +1379,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1412,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123233568</v>
+        <v>123233772</v>
       </c>
       <c r="B8" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,36 +1432,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1466,13 +1461,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441564</v>
+        <v>441598</v>
       </c>
       <c r="R8" t="n">
-        <v>7028721</v>
+        <v>7028738</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1506,7 +1501,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1521,6 +1516,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1538,7 +1553,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123234752</v>
+        <v>123236127</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1578,13 +1593,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441583</v>
+        <v>441667</v>
       </c>
       <c r="R9" t="n">
-        <v>7028658</v>
+        <v>7028798</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1618,7 +1633,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1670,10 +1685,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123236259</v>
+        <v>123235545</v>
       </c>
       <c r="B10" t="n">
-        <v>97319</v>
+        <v>97325</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1686,16 +1701,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1715,13 +1730,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441633</v>
+        <v>441587</v>
       </c>
       <c r="R10" t="n">
-        <v>7028804</v>
+        <v>7028776</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1761,6 +1776,11 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1777,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123233597</v>
+        <v>123234252</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,25 +1809,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1817,13 +1837,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441569</v>
+        <v>441667</v>
       </c>
       <c r="R11" t="n">
-        <v>7028701</v>
+        <v>7028689</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1863,31 +1883,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1904,7 +1899,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123233043</v>
+        <v>123233597</v>
       </c>
       <c r="B12" t="n">
         <v>78766</v>
@@ -1944,13 +1939,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441571</v>
+        <v>441569</v>
       </c>
       <c r="R12" t="n">
-        <v>7028720</v>
+        <v>7028701</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2031,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123234252</v>
+        <v>123234048</v>
       </c>
       <c r="B13" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2043,25 +2038,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2071,13 +2066,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441667</v>
+        <v>441630</v>
       </c>
       <c r="R13" t="n">
-        <v>7028689</v>
+        <v>7028692</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2109,6 +2104,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2117,6 +2117,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2240,7 +2265,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123236343</v>
+        <v>123235031</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2276,14 +2301,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441640</v>
+        <v>441542</v>
       </c>
       <c r="R15" t="n">
-        <v>7028845</v>
+        <v>7028672</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2318,6 +2343,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2344,12 +2374,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2367,7 +2397,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123234048</v>
+        <v>123233946</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2407,13 +2437,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441630</v>
+        <v>441609</v>
       </c>
       <c r="R16" t="n">
-        <v>7028692</v>
+        <v>7028716</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2447,7 +2477,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2499,10 +2529,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235031</v>
+        <v>123236259</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2511,38 +2541,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441542</v>
+        <v>441633</v>
       </c>
       <c r="R17" t="n">
-        <v>7028672</v>
+        <v>7028804</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2577,11 +2612,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2590,31 +2620,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2631,7 +2636,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123233946</v>
+        <v>123235901</v>
       </c>
       <c r="B18" t="n">
         <v>78766</v>
@@ -2671,13 +2676,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441609</v>
+        <v>441683</v>
       </c>
       <c r="R18" t="n">
-        <v>7028716</v>
+        <v>7028765</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2711,7 +2716,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2763,7 +2768,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236631</v>
+        <v>123234752</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2799,14 +2804,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441559</v>
+        <v>441583</v>
       </c>
       <c r="R19" t="n">
-        <v>7028811</v>
+        <v>7028658</v>
       </c>
       <c r="S19" t="n">
         <v>9</v>
@@ -2841,6 +2846,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På en gammal gran intill ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2852,7 +2862,7 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
@@ -2890,7 +2900,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123235689</v>
+        <v>123236343</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2926,14 +2936,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441596</v>
+        <v>441640</v>
       </c>
       <c r="R20" t="n">
-        <v>7028775</v>
+        <v>7028845</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -2994,12 +3004,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3017,7 +3027,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123233772</v>
+        <v>123236631</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -3051,24 +3061,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441598</v>
+        <v>441559</v>
       </c>
       <c r="R21" t="n">
-        <v>7028738</v>
+        <v>7028811</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3100,11 +3105,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123233568</v>
+        <v>123236343</v>
       </c>
       <c r="B4" t="n">
-        <v>57631</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,51 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441564</v>
+        <v>441640</v>
       </c>
       <c r="R4" t="n">
-        <v>7028721</v>
+        <v>7028845</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,11 +987,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1018,6 +999,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1035,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123233043</v>
+        <v>123235737</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,13 +1076,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441571</v>
+        <v>441617</v>
       </c>
       <c r="R5" t="n">
-        <v>7028720</v>
+        <v>7028768</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1162,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123235689</v>
+        <v>123233568</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,37 +1179,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441596</v>
+        <v>441564</v>
       </c>
       <c r="R6" t="n">
-        <v>7028775</v>
+        <v>7028721</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1240,6 +1255,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1252,26 +1272,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1289,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123235737</v>
+        <v>123235031</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1329,13 +1329,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441617</v>
+        <v>441542</v>
       </c>
       <c r="R7" t="n">
-        <v>7028768</v>
+        <v>7028672</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,6 +1365,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1416,10 +1421,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123233772</v>
+        <v>123233043</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1450,21 +1455,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441598</v>
+        <v>441571</v>
       </c>
       <c r="R8" t="n">
-        <v>7028738</v>
+        <v>7028720</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1497,11 +1497,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1553,10 +1548,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123236127</v>
+        <v>123233597</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1593,13 +1588,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441667</v>
+        <v>441569</v>
       </c>
       <c r="R9" t="n">
-        <v>7028798</v>
+        <v>7028701</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1629,11 +1624,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1685,10 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123235545</v>
+        <v>123236460</v>
       </c>
       <c r="B10" t="n">
-        <v>97325</v>
+        <v>97322</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1701,16 +1691,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1726,17 +1716,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441587</v>
+        <v>441626</v>
       </c>
       <c r="R10" t="n">
-        <v>7028776</v>
+        <v>7028860</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1776,11 +1766,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1797,10 +1782,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123234252</v>
+        <v>123234752</v>
       </c>
       <c r="B11" t="n">
-        <v>97319</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1809,25 +1794,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1837,13 +1822,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441667</v>
+        <v>441583</v>
       </c>
       <c r="R11" t="n">
-        <v>7028689</v>
+        <v>7028658</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1875,6 +1860,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På en gammal gran intill ett fuktstråk.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1883,6 +1873,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1899,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123233597</v>
+        <v>123235545</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>97328</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,41 +1926,46 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441569</v>
+        <v>441587</v>
       </c>
       <c r="R12" t="n">
-        <v>7028701</v>
+        <v>7028776</v>
       </c>
       <c r="S12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1989,26 +2009,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2026,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123234048</v>
+        <v>123235901</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2066,13 +2066,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441630</v>
+        <v>441683</v>
       </c>
       <c r="R13" t="n">
-        <v>7028692</v>
+        <v>7028765</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,10 +2158,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123236460</v>
+        <v>123236127</v>
       </c>
       <c r="B14" t="n">
-        <v>97319</v>
+        <v>78769</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2170,46 +2170,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441626</v>
+        <v>441667</v>
       </c>
       <c r="R14" t="n">
-        <v>7028860</v>
+        <v>7028798</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2241,6 +2236,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2249,6 +2249,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2265,10 +2290,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123235031</v>
+        <v>123233946</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2305,10 +2330,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441542</v>
+        <v>441609</v>
       </c>
       <c r="R15" t="n">
-        <v>7028672</v>
+        <v>7028716</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2345,7 +2370,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2397,10 +2422,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123233946</v>
+        <v>123236259</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>97322</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2409,38 +2434,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441609</v>
+        <v>441633</v>
       </c>
       <c r="R16" t="n">
-        <v>7028716</v>
+        <v>7028804</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2475,11 +2505,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2488,31 +2513,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2529,10 +2529,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236259</v>
+        <v>123234252</v>
       </c>
       <c r="B17" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2563,21 +2563,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441633</v>
+        <v>441667</v>
       </c>
       <c r="R17" t="n">
-        <v>7028804</v>
+        <v>7028689</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2636,10 +2631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123235901</v>
+        <v>123233772</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2670,19 +2665,24 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441683</v>
+        <v>441598</v>
       </c>
       <c r="R18" t="n">
-        <v>7028765</v>
+        <v>7028738</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gammal gran.</t>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2768,10 +2768,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123234752</v>
+        <v>123235689</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2808,13 +2808,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441583</v>
+        <v>441596</v>
       </c>
       <c r="R19" t="n">
-        <v>7028658</v>
+        <v>7028775</v>
       </c>
       <c r="S19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2844,11 +2844,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2900,10 +2895,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123236343</v>
+        <v>123236631</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2940,13 +2935,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441640</v>
+        <v>441559</v>
       </c>
       <c r="R20" t="n">
-        <v>7028845</v>
+        <v>7028811</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2989,7 +2984,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3004,12 +2999,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3027,10 +3022,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123236631</v>
+        <v>123234048</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3063,14 +3058,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441559</v>
+        <v>441630</v>
       </c>
       <c r="R21" t="n">
-        <v>7028811</v>
+        <v>7028692</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3105,6 +3100,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236343</v>
+        <v>123233568</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +925,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441640</v>
+        <v>441564</v>
       </c>
       <c r="R4" t="n">
-        <v>7028845</v>
+        <v>7028721</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,6 +1001,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -999,26 +1018,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1039,7 +1038,7 @@
         <v>123235737</v>
       </c>
       <c r="B5" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1163,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123233568</v>
+        <v>123236259</v>
       </c>
       <c r="B6" t="n">
-        <v>57634</v>
+        <v>97324</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,40 +1174,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1217,13 +1207,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441564</v>
+        <v>441633</v>
       </c>
       <c r="R6" t="n">
-        <v>7028721</v>
+        <v>7028804</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1255,11 +1245,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1268,11 +1253,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1289,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123235031</v>
+        <v>123233597</v>
       </c>
       <c r="B7" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1329,13 +1309,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441542</v>
+        <v>441569</v>
       </c>
       <c r="R7" t="n">
-        <v>7028672</v>
+        <v>7028701</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,11 +1345,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1421,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123233043</v>
+        <v>123236343</v>
       </c>
       <c r="B8" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1457,14 +1432,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441571</v>
+        <v>441640</v>
       </c>
       <c r="R8" t="n">
-        <v>7028720</v>
+        <v>7028845</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1525,12 +1500,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1548,10 +1523,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123233597</v>
+        <v>123236460</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>97324</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1560,38 +1535,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441569</v>
+        <v>441626</v>
       </c>
       <c r="R9" t="n">
-        <v>7028701</v>
+        <v>7028860</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1634,31 +1614,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1675,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123236460</v>
+        <v>123234048</v>
       </c>
       <c r="B10" t="n">
-        <v>97322</v>
+        <v>78771</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,43 +1642,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441626</v>
+        <v>441630</v>
       </c>
       <c r="R10" t="n">
-        <v>7028860</v>
+        <v>7028692</v>
       </c>
       <c r="S10" t="n">
         <v>9</v>
@@ -1758,6 +1708,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1766,6 +1721,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1782,10 +1762,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123234752</v>
+        <v>123233043</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1822,13 +1802,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441583</v>
+        <v>441571</v>
       </c>
       <c r="R11" t="n">
-        <v>7028658</v>
+        <v>7028720</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1858,11 +1838,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,7 +1892,7 @@
         <v>123235545</v>
       </c>
       <c r="B12" t="n">
-        <v>97328</v>
+        <v>97330</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2026,10 +2001,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123235901</v>
+        <v>123234252</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>97324</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2038,25 +2013,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2066,13 +2041,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441683</v>
+        <v>441667</v>
       </c>
       <c r="R13" t="n">
-        <v>7028765</v>
+        <v>7028689</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2104,11 +2079,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2117,31 +2087,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2158,10 +2103,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123236127</v>
+        <v>123233772</v>
       </c>
       <c r="B14" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2192,16 +2137,21 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441667</v>
+        <v>441598</v>
       </c>
       <c r="R14" t="n">
-        <v>7028798</v>
+        <v>7028738</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2238,7 +2188,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2290,10 +2240,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123233946</v>
+        <v>123236127</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2330,10 +2280,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441609</v>
+        <v>441667</v>
       </c>
       <c r="R15" t="n">
-        <v>7028716</v>
+        <v>7028798</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2370,7 +2320,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2422,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236259</v>
+        <v>123233946</v>
       </c>
       <c r="B16" t="n">
-        <v>97322</v>
+        <v>78771</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2434,43 +2384,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441633</v>
+        <v>441609</v>
       </c>
       <c r="R16" t="n">
-        <v>7028804</v>
+        <v>7028716</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2505,6 +2450,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2513,6 +2463,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2529,10 +2504,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123234252</v>
+        <v>123235901</v>
       </c>
       <c r="B17" t="n">
-        <v>97322</v>
+        <v>78771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2541,25 +2516,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2569,13 +2544,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441667</v>
+        <v>441683</v>
       </c>
       <c r="R17" t="n">
-        <v>7028689</v>
+        <v>7028765</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2607,6 +2582,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2615,6 +2595,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2631,10 +2636,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123233772</v>
+        <v>123234752</v>
       </c>
       <c r="B18" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2665,24 +2670,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441598</v>
+        <v>441583</v>
       </c>
       <c r="R18" t="n">
-        <v>7028738</v>
+        <v>7028658</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2771,7 +2771,7 @@
         <v>123235689</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2895,10 +2895,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123236631</v>
+        <v>123235031</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2931,17 +2931,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441559</v>
+        <v>441542</v>
       </c>
       <c r="R20" t="n">
-        <v>7028811</v>
+        <v>7028672</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2973,6 +2973,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2984,7 +2989,7 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
@@ -3022,10 +3027,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123234048</v>
+        <v>123236631</v>
       </c>
       <c r="B21" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3058,14 +3063,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441630</v>
+        <v>441559</v>
       </c>
       <c r="R21" t="n">
-        <v>7028692</v>
+        <v>7028811</v>
       </c>
       <c r="S21" t="n">
         <v>9</v>
@@ -3100,11 +3105,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123235737</v>
+        <v>123236259</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>97324</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,41 +1047,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441617</v>
+        <v>441633</v>
       </c>
       <c r="R5" t="n">
-        <v>7028768</v>
+        <v>7028804</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1121,31 +1126,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1162,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236259</v>
+        <v>123235737</v>
       </c>
       <c r="B6" t="n">
-        <v>97324</v>
+        <v>78771</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1174,46 +1154,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441633</v>
+        <v>441617</v>
       </c>
       <c r="R6" t="n">
-        <v>7028804</v>
+        <v>7028768</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,6 +1228,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1889,10 +1889,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123235545</v>
+        <v>123233772</v>
       </c>
       <c r="B12" t="n">
-        <v>97330</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1901,31 +1901,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441587</v>
+        <v>441598</v>
       </c>
       <c r="R12" t="n">
-        <v>7028776</v>
+        <v>7028738</v>
       </c>
       <c r="S12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1972,6 +1972,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1984,6 +1989,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2001,10 +2026,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123234252</v>
+        <v>123236127</v>
       </c>
       <c r="B13" t="n">
-        <v>97324</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2013,25 +2038,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2044,7 +2069,7 @@
         <v>441667</v>
       </c>
       <c r="R13" t="n">
-        <v>7028689</v>
+        <v>7028798</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2079,6 +2104,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2087,6 +2117,31 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2103,7 +2158,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123233772</v>
+        <v>123233946</v>
       </c>
       <c r="B14" t="n">
         <v>78771</v>
@@ -2137,21 +2192,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441598</v>
+        <v>441609</v>
       </c>
       <c r="R14" t="n">
-        <v>7028738</v>
+        <v>7028716</v>
       </c>
       <c r="S14" t="n">
         <v>8</v>
@@ -2188,7 +2238,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2240,10 +2290,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123236127</v>
+        <v>123235545</v>
       </c>
       <c r="B15" t="n">
-        <v>78771</v>
+        <v>97330</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2252,41 +2302,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441667</v>
+        <v>441587</v>
       </c>
       <c r="R15" t="n">
-        <v>7028798</v>
+        <v>7028776</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2318,11 +2373,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2335,26 +2385,6 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2372,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123233946</v>
+        <v>123234252</v>
       </c>
       <c r="B16" t="n">
-        <v>78771</v>
+        <v>97324</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2384,25 +2414,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2412,10 +2442,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441609</v>
+        <v>441667</v>
       </c>
       <c r="R16" t="n">
-        <v>7028716</v>
+        <v>7028689</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2450,11 +2480,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gammal gran.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2463,31 +2488,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123233568</v>
+        <v>123235901</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,51 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441564</v>
+        <v>441683</v>
       </c>
       <c r="R4" t="n">
-        <v>7028721</v>
+        <v>7028765</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,6 +1004,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1035,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123236259</v>
+        <v>123235689</v>
       </c>
       <c r="B5" t="n">
-        <v>97324</v>
+        <v>78772</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,43 +1053,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441633</v>
+        <v>441596</v>
       </c>
       <c r="R5" t="n">
-        <v>7028804</v>
+        <v>7028775</v>
       </c>
       <c r="S5" t="n">
         <v>8</v>
@@ -1126,6 +1127,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1145,7 +1171,7 @@
         <v>123235737</v>
       </c>
       <c r="B6" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1269,10 +1295,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123233597</v>
+        <v>123236631</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,14 +1331,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441569</v>
+        <v>441559</v>
       </c>
       <c r="R7" t="n">
-        <v>7028701</v>
+        <v>7028811</v>
       </c>
       <c r="S7" t="n">
         <v>9</v>
@@ -1358,7 +1384,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1396,10 +1422,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123236343</v>
+        <v>123236259</v>
       </c>
       <c r="B8" t="n">
-        <v>78771</v>
+        <v>97330</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,38 +1434,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441640</v>
+        <v>441633</v>
       </c>
       <c r="R8" t="n">
-        <v>7028845</v>
+        <v>7028804</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1482,31 +1513,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1523,10 +1529,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123236460</v>
+        <v>123236343</v>
       </c>
       <c r="B9" t="n">
-        <v>97324</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1535,46 +1541,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441626</v>
+        <v>441640</v>
       </c>
       <c r="R9" t="n">
-        <v>7028860</v>
+        <v>7028845</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1614,6 +1615,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1630,10 +1656,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123234048</v>
+        <v>123235545</v>
       </c>
       <c r="B10" t="n">
-        <v>78771</v>
+        <v>97336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1642,41 +1668,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441630</v>
+        <v>441587</v>
       </c>
       <c r="R10" t="n">
-        <v>7028692</v>
+        <v>7028776</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,11 +1739,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1725,26 +1751,6 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1762,10 +1768,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123233043</v>
+        <v>123236460</v>
       </c>
       <c r="B11" t="n">
-        <v>78771</v>
+        <v>97330</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1774,41 +1780,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441571</v>
+        <v>441626</v>
       </c>
       <c r="R11" t="n">
-        <v>7028720</v>
+        <v>7028860</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1848,31 +1859,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1889,10 +1875,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123233772</v>
+        <v>123233946</v>
       </c>
       <c r="B12" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1923,21 +1909,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441598</v>
+        <v>441609</v>
       </c>
       <c r="R12" t="n">
-        <v>7028738</v>
+        <v>7028716</v>
       </c>
       <c r="S12" t="n">
         <v>8</v>
@@ -1974,7 +1955,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2026,10 +2007,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123236127</v>
+        <v>123233597</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2066,13 +2047,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441667</v>
+        <v>441569</v>
       </c>
       <c r="R13" t="n">
-        <v>7028798</v>
+        <v>7028701</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2102,11 +2083,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2158,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123233946</v>
+        <v>123234752</v>
       </c>
       <c r="B14" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2198,13 +2174,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441609</v>
+        <v>441583</v>
       </c>
       <c r="R14" t="n">
-        <v>7028716</v>
+        <v>7028658</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2238,7 +2214,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2290,10 +2266,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123235545</v>
+        <v>123236127</v>
       </c>
       <c r="B15" t="n">
-        <v>97330</v>
+        <v>78772</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2302,46 +2278,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441587</v>
+        <v>441667</v>
       </c>
       <c r="R15" t="n">
-        <v>7028776</v>
+        <v>7028798</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2373,6 +2344,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2385,6 +2361,26 @@
       <c r="AH15" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2405,7 +2401,7 @@
         <v>123234252</v>
       </c>
       <c r="B16" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2504,10 +2500,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235901</v>
+        <v>123233043</v>
       </c>
       <c r="B17" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2544,13 +2540,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441683</v>
+        <v>441571</v>
       </c>
       <c r="R17" t="n">
-        <v>7028765</v>
+        <v>7028720</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2580,11 +2576,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2636,10 +2627,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123234752</v>
+        <v>123233568</v>
       </c>
       <c r="B18" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2652,37 +2643,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441583</v>
+        <v>441564</v>
       </c>
       <c r="R18" t="n">
-        <v>7028658</v>
+        <v>7028721</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2716,7 +2721,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2731,26 +2736,6 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2768,10 +2753,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123235689</v>
+        <v>123235031</v>
       </c>
       <c r="B19" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2808,10 +2793,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441596</v>
+        <v>441542</v>
       </c>
       <c r="R19" t="n">
-        <v>7028775</v>
+        <v>7028672</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2844,6 +2829,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2895,10 +2885,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123235031</v>
+        <v>123234048</v>
       </c>
       <c r="B20" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2935,13 +2925,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441542</v>
+        <v>441630</v>
       </c>
       <c r="R20" t="n">
-        <v>7028672</v>
+        <v>7028692</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2975,7 +2965,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3027,10 +3017,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123236631</v>
+        <v>123233772</v>
       </c>
       <c r="B21" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3061,19 +3051,24 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441559</v>
+        <v>441598</v>
       </c>
       <c r="R21" t="n">
-        <v>7028811</v>
+        <v>7028738</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3105,6 +3100,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3116,7 +3116,7 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123235901</v>
+        <v>123233568</v>
       </c>
       <c r="B4" t="n">
-        <v>78772</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +925,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441683</v>
+        <v>441564</v>
       </c>
       <c r="R4" t="n">
-        <v>7028765</v>
+        <v>7028721</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -989,7 +1003,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gammal gran.</t>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,26 +1018,6 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123235689</v>
+        <v>123235545</v>
       </c>
       <c r="B5" t="n">
-        <v>78772</v>
+        <v>97339</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1053,41 +1047,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441596</v>
+        <v>441587</v>
       </c>
       <c r="R5" t="n">
-        <v>7028775</v>
+        <v>7028776</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,26 +1130,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1168,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123235737</v>
+        <v>123236460</v>
       </c>
       <c r="B6" t="n">
-        <v>78772</v>
+        <v>97333</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,41 +1159,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441617</v>
+        <v>441626</v>
       </c>
       <c r="R6" t="n">
-        <v>7028768</v>
+        <v>7028860</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1254,31 +1238,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1295,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123236631</v>
+        <v>123235689</v>
       </c>
       <c r="B7" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1331,17 +1290,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441559</v>
+        <v>441596</v>
       </c>
       <c r="R7" t="n">
-        <v>7028811</v>
+        <v>7028775</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1384,7 +1343,7 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -1422,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123236259</v>
+        <v>123233597</v>
       </c>
       <c r="B8" t="n">
-        <v>97330</v>
+        <v>78775</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1434,46 +1393,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441633</v>
+        <v>441569</v>
       </c>
       <c r="R8" t="n">
-        <v>7028804</v>
+        <v>7028701</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1513,6 +1467,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1529,10 +1508,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123236343</v>
+        <v>123236127</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1565,14 +1544,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441640</v>
+        <v>441667</v>
       </c>
       <c r="R9" t="n">
-        <v>7028845</v>
+        <v>7028798</v>
       </c>
       <c r="S9" t="n">
         <v>8</v>
@@ -1607,6 +1586,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1633,12 +1617,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1656,10 +1640,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123235545</v>
+        <v>123233946</v>
       </c>
       <c r="B10" t="n">
-        <v>97336</v>
+        <v>78775</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1668,46 +1652,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441587</v>
+        <v>441609</v>
       </c>
       <c r="R10" t="n">
-        <v>7028776</v>
+        <v>7028716</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,6 +1718,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1751,6 +1735,26 @@
       <c r="AH10" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1768,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123236460</v>
+        <v>123233043</v>
       </c>
       <c r="B11" t="n">
-        <v>97330</v>
+        <v>78775</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,46 +1784,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441626</v>
+        <v>441571</v>
       </c>
       <c r="R11" t="n">
-        <v>7028860</v>
+        <v>7028720</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1859,6 +1858,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1875,10 +1899,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123233946</v>
+        <v>123235901</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1915,13 +1939,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441609</v>
+        <v>441683</v>
       </c>
       <c r="R12" t="n">
-        <v>7028716</v>
+        <v>7028765</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1955,7 +1979,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2007,10 +2031,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123233597</v>
+        <v>123234048</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2047,10 +2071,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441569</v>
+        <v>441630</v>
       </c>
       <c r="R13" t="n">
-        <v>7028701</v>
+        <v>7028692</v>
       </c>
       <c r="S13" t="n">
         <v>9</v>
@@ -2083,6 +2107,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2163,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123234752</v>
+        <v>123236631</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2170,14 +2199,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441583</v>
+        <v>441559</v>
       </c>
       <c r="R14" t="n">
-        <v>7028658</v>
+        <v>7028811</v>
       </c>
       <c r="S14" t="n">
         <v>9</v>
@@ -2212,11 +2241,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2228,7 +2252,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -2266,10 +2290,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123236127</v>
+        <v>123234752</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2306,13 +2330,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441667</v>
+        <v>441583</v>
       </c>
       <c r="R15" t="n">
-        <v>7028798</v>
+        <v>7028658</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2346,7 +2370,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2398,10 +2422,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123234252</v>
+        <v>123235737</v>
       </c>
       <c r="B16" t="n">
-        <v>97330</v>
+        <v>78775</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2410,25 +2434,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2438,13 +2462,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441667</v>
+        <v>441617</v>
       </c>
       <c r="R16" t="n">
-        <v>7028689</v>
+        <v>7028768</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2484,6 +2508,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2500,10 +2549,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123233043</v>
+        <v>123235031</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2540,10 +2589,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441571</v>
+        <v>441542</v>
       </c>
       <c r="R17" t="n">
-        <v>7028720</v>
+        <v>7028672</v>
       </c>
       <c r="S17" t="n">
         <v>8</v>
@@ -2576,6 +2625,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2627,10 +2681,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123233568</v>
+        <v>123233772</v>
       </c>
       <c r="B18" t="n">
-        <v>57634</v>
+        <v>78775</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2643,36 +2697,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2681,13 +2726,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441564</v>
+        <v>441598</v>
       </c>
       <c r="R18" t="n">
-        <v>7028721</v>
+        <v>7028738</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2721,7 +2766,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2736,6 +2781,26 @@
       <c r="AH18" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2753,10 +2818,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123235031</v>
+        <v>123236343</v>
       </c>
       <c r="B19" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2789,14 +2854,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441542</v>
+        <v>441640</v>
       </c>
       <c r="R19" t="n">
-        <v>7028672</v>
+        <v>7028845</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2831,11 +2896,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2862,12 +2922,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2885,10 +2945,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123234048</v>
+        <v>123234252</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>97333</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2897,25 +2957,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2925,13 +2985,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441630</v>
+        <v>441667</v>
       </c>
       <c r="R20" t="n">
-        <v>7028692</v>
+        <v>7028689</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2963,11 +3023,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2976,31 +3031,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3017,10 +3047,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123233772</v>
+        <v>123236259</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>97333</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3029,31 +3059,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -3062,10 +3092,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441598</v>
+        <v>441633</v>
       </c>
       <c r="R21" t="n">
-        <v>7028738</v>
+        <v>7028804</v>
       </c>
       <c r="S21" t="n">
         <v>8</v>
@@ -3100,11 +3130,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3113,31 +3138,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>123233568</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123235545</v>
+        <v>123235689</v>
       </c>
       <c r="B5" t="n">
-        <v>97339</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,46 +1047,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441587</v>
+        <v>441596</v>
       </c>
       <c r="R5" t="n">
-        <v>7028776</v>
+        <v>7028775</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1130,6 +1125,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1147,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236460</v>
+        <v>123236343</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>78781</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,46 +1174,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441626</v>
+        <v>441640</v>
       </c>
       <c r="R6" t="n">
-        <v>7028860</v>
+        <v>7028845</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,6 +1248,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1254,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123235689</v>
+        <v>123233043</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1294,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441596</v>
+        <v>441571</v>
       </c>
       <c r="R7" t="n">
-        <v>7028775</v>
+        <v>7028720</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1381,10 +1416,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123233597</v>
+        <v>123236631</v>
       </c>
       <c r="B8" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,14 +1452,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441569</v>
+        <v>441559</v>
       </c>
       <c r="R8" t="n">
-        <v>7028701</v>
+        <v>7028811</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1470,7 +1505,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -1508,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123236127</v>
+        <v>123236460</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>97350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1520,41 +1555,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441667</v>
+        <v>441626</v>
       </c>
       <c r="R9" t="n">
-        <v>7028798</v>
+        <v>7028860</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1586,11 +1626,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1599,31 +1634,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1640,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123233946</v>
+        <v>123233772</v>
       </c>
       <c r="B10" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1674,16 +1684,21 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441609</v>
+        <v>441598</v>
       </c>
       <c r="R10" t="n">
-        <v>7028716</v>
+        <v>7028738</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1720,7 +1735,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,10 +1787,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123233043</v>
+        <v>123233597</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1812,13 +1827,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441571</v>
+        <v>441569</v>
       </c>
       <c r="R11" t="n">
-        <v>7028720</v>
+        <v>7028701</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1899,10 +1914,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123235901</v>
+        <v>123234252</v>
       </c>
       <c r="B12" t="n">
-        <v>78775</v>
+        <v>97350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1911,25 +1926,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1939,13 +1954,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441683</v>
+        <v>441667</v>
       </c>
       <c r="R12" t="n">
-        <v>7028765</v>
+        <v>7028689</v>
       </c>
       <c r="S12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1977,11 +1992,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1990,31 +2000,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2034,7 +2019,7 @@
         <v>123234048</v>
       </c>
       <c r="B13" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2163,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123236631</v>
+        <v>123235545</v>
       </c>
       <c r="B14" t="n">
-        <v>78775</v>
+        <v>97356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2175,41 +2160,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441559</v>
+        <v>441587</v>
       </c>
       <c r="R14" t="n">
-        <v>7028811</v>
+        <v>7028776</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2252,27 +2242,7 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2290,10 +2260,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123234752</v>
+        <v>123233946</v>
       </c>
       <c r="B15" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2330,13 +2300,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441583</v>
+        <v>441609</v>
       </c>
       <c r="R15" t="n">
-        <v>7028658</v>
+        <v>7028716</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2370,7 +2340,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2422,10 +2392,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123235737</v>
+        <v>123234752</v>
       </c>
       <c r="B16" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2462,13 +2432,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441617</v>
+        <v>441583</v>
       </c>
       <c r="R16" t="n">
-        <v>7028768</v>
+        <v>7028658</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2498,6 +2468,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2549,10 +2524,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235031</v>
+        <v>123235901</v>
       </c>
       <c r="B17" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2589,13 +2564,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441542</v>
+        <v>441683</v>
       </c>
       <c r="R17" t="n">
-        <v>7028672</v>
+        <v>7028765</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2629,7 +2604,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2681,10 +2656,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123233772</v>
+        <v>123236127</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2715,21 +2690,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441598</v>
+        <v>441667</v>
       </c>
       <c r="R18" t="n">
-        <v>7028738</v>
+        <v>7028798</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2766,7 +2736,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2818,10 +2788,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236343</v>
+        <v>123236259</v>
       </c>
       <c r="B19" t="n">
-        <v>78775</v>
+        <v>97350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2830,38 +2800,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441640</v>
+        <v>441633</v>
       </c>
       <c r="R19" t="n">
-        <v>7028845</v>
+        <v>7028804</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2904,31 +2879,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2945,10 +2895,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123234252</v>
+        <v>123235031</v>
       </c>
       <c r="B20" t="n">
-        <v>97333</v>
+        <v>78781</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2957,25 +2907,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2985,10 +2935,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441667</v>
+        <v>441542</v>
       </c>
       <c r="R20" t="n">
-        <v>7028689</v>
+        <v>7028672</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -3023,6 +2973,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3031,6 +2986,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -3047,10 +3027,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123236259</v>
+        <v>123235737</v>
       </c>
       <c r="B21" t="n">
-        <v>97333</v>
+        <v>78781</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3059,46 +3039,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441633</v>
+        <v>441617</v>
       </c>
       <c r="R21" t="n">
-        <v>7028804</v>
+        <v>7028768</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3138,6 +3113,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -1543,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123236460</v>
+        <v>123233772</v>
       </c>
       <c r="B9" t="n">
-        <v>97350</v>
+        <v>78781</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,46 +1555,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441626</v>
+        <v>441598</v>
       </c>
       <c r="R9" t="n">
-        <v>7028860</v>
+        <v>7028738</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1626,6 +1626,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1634,6 +1639,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1650,10 +1680,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123233772</v>
+        <v>123236460</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>97350</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1662,46 +1692,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441598</v>
+        <v>441626</v>
       </c>
       <c r="R10" t="n">
-        <v>7028738</v>
+        <v>7028860</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1733,11 +1763,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1746,31 +1771,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -2524,10 +2524,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235901</v>
+        <v>123236259</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>97350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2536,41 +2536,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441683</v>
+        <v>441633</v>
       </c>
       <c r="R17" t="n">
-        <v>7028765</v>
+        <v>7028804</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,11 +2607,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2615,31 +2615,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2656,7 +2631,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123236127</v>
+        <v>123235901</v>
       </c>
       <c r="B18" t="n">
         <v>78781</v>
@@ -2696,13 +2671,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441667</v>
+        <v>441683</v>
       </c>
       <c r="R18" t="n">
-        <v>7028798</v>
+        <v>7028765</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2736,7 +2711,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2788,10 +2763,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236259</v>
+        <v>123236127</v>
       </c>
       <c r="B19" t="n">
-        <v>97350</v>
+        <v>78781</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2800,43 +2775,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441633</v>
+        <v>441667</v>
       </c>
       <c r="R19" t="n">
-        <v>7028804</v>
+        <v>7028798</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2871,6 +2841,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2879,6 +2854,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -1543,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123233772</v>
+        <v>123236460</v>
       </c>
       <c r="B9" t="n">
-        <v>78781</v>
+        <v>97350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,46 +1555,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441598</v>
+        <v>441626</v>
       </c>
       <c r="R9" t="n">
-        <v>7028738</v>
+        <v>7028860</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1626,11 +1626,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1639,31 +1634,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1680,10 +1650,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123236460</v>
+        <v>123233772</v>
       </c>
       <c r="B10" t="n">
-        <v>97350</v>
+        <v>78781</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1692,46 +1662,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441626</v>
+        <v>441598</v>
       </c>
       <c r="R10" t="n">
-        <v>7028860</v>
+        <v>7028738</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1763,6 +1733,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1771,6 +1746,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -2524,10 +2524,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236259</v>
+        <v>123235901</v>
       </c>
       <c r="B17" t="n">
-        <v>97350</v>
+        <v>78781</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2536,46 +2536,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441633</v>
+        <v>441683</v>
       </c>
       <c r="R17" t="n">
-        <v>7028804</v>
+        <v>7028765</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2607,6 +2602,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2615,6 +2615,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2631,7 +2656,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123235901</v>
+        <v>123236127</v>
       </c>
       <c r="B18" t="n">
         <v>78781</v>
@@ -2671,13 +2696,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441683</v>
+        <v>441667</v>
       </c>
       <c r="R18" t="n">
-        <v>7028765</v>
+        <v>7028798</v>
       </c>
       <c r="S18" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2711,7 +2736,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar på en gammal gran.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2763,10 +2788,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236127</v>
+        <v>123236259</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>97350</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2775,38 +2800,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441667</v>
+        <v>441633</v>
       </c>
       <c r="R19" t="n">
-        <v>7028798</v>
+        <v>7028804</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2841,11 +2871,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2854,31 +2879,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123233568</v>
+        <v>123233946</v>
       </c>
       <c r="B4" t="n">
-        <v>57640</v>
+        <v>78786</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,51 +925,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441564</v>
+        <v>441609</v>
       </c>
       <c r="R4" t="n">
-        <v>7028721</v>
+        <v>7028716</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1003,7 +989,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,6 +1004,26 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1035,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123235689</v>
+        <v>123234752</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1075,13 +1081,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441596</v>
+        <v>441583</v>
       </c>
       <c r="R5" t="n">
-        <v>7028775</v>
+        <v>7028658</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,6 +1117,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1162,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123236343</v>
+        <v>123233597</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1198,17 +1209,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441640</v>
+        <v>441569</v>
       </c>
       <c r="R6" t="n">
-        <v>7028845</v>
+        <v>7028701</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1266,12 +1277,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1289,10 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123233043</v>
+        <v>123235689</v>
       </c>
       <c r="B7" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1329,10 +1340,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441571</v>
+        <v>441596</v>
       </c>
       <c r="R7" t="n">
-        <v>7028720</v>
+        <v>7028775</v>
       </c>
       <c r="S7" t="n">
         <v>8</v>
@@ -1416,10 +1427,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123236631</v>
+        <v>123235545</v>
       </c>
       <c r="B8" t="n">
-        <v>78781</v>
+        <v>97373</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1428,41 +1439,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441559</v>
+        <v>441587</v>
       </c>
       <c r="R8" t="n">
-        <v>7028811</v>
+        <v>7028776</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1505,27 +1521,7 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1543,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123236460</v>
+        <v>123236631</v>
       </c>
       <c r="B9" t="n">
-        <v>97350</v>
+        <v>78786</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,43 +1551,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441626</v>
+        <v>441559</v>
       </c>
       <c r="R9" t="n">
-        <v>7028860</v>
+        <v>7028811</v>
       </c>
       <c r="S9" t="n">
         <v>9</v>
@@ -1634,6 +1625,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1650,10 +1666,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123233772</v>
+        <v>123236343</v>
       </c>
       <c r="B10" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1684,21 +1700,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441598</v>
+        <v>441640</v>
       </c>
       <c r="R10" t="n">
-        <v>7028738</v>
+        <v>7028845</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1733,11 +1744,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1764,12 +1770,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1787,10 +1793,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123233597</v>
+        <v>123235737</v>
       </c>
       <c r="B11" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1827,13 +1833,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441569</v>
+        <v>441617</v>
       </c>
       <c r="R11" t="n">
-        <v>7028701</v>
+        <v>7028768</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1914,10 +1920,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123234252</v>
+        <v>123233568</v>
       </c>
       <c r="B12" t="n">
-        <v>97350</v>
+        <v>57643</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1926,41 +1932,55 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441667</v>
+        <v>441564</v>
       </c>
       <c r="R12" t="n">
-        <v>7028689</v>
+        <v>7028721</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1992,6 +2012,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2000,6 +2025,11 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2016,10 +2046,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123234048</v>
+        <v>123233772</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2050,19 +2080,24 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441630</v>
+        <v>441598</v>
       </c>
       <c r="R13" t="n">
-        <v>7028692</v>
+        <v>7028738</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2096,7 +2131,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,10 +2183,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123235545</v>
+        <v>123235901</v>
       </c>
       <c r="B14" t="n">
-        <v>97356</v>
+        <v>78786</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,46 +2195,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441587</v>
+        <v>441683</v>
       </c>
       <c r="R14" t="n">
-        <v>7028776</v>
+        <v>7028765</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2231,6 +2261,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2243,6 +2278,26 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2260,10 +2315,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123233946</v>
+        <v>123234048</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2300,13 +2355,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441609</v>
+        <v>441630</v>
       </c>
       <c r="R15" t="n">
-        <v>7028716</v>
+        <v>7028692</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2340,7 +2395,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2392,10 +2447,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123234752</v>
+        <v>123236127</v>
       </c>
       <c r="B16" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2432,13 +2487,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441583</v>
+        <v>441667</v>
       </c>
       <c r="R16" t="n">
-        <v>7028658</v>
+        <v>7028798</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2472,7 +2527,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2524,10 +2579,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235901</v>
+        <v>123236259</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>97367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2536,41 +2591,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441683</v>
+        <v>441633</v>
       </c>
       <c r="R17" t="n">
-        <v>7028765</v>
+        <v>7028804</v>
       </c>
       <c r="S17" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2602,11 +2662,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2615,31 +2670,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2656,10 +2686,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123236127</v>
+        <v>123235031</v>
       </c>
       <c r="B18" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2696,10 +2726,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441667</v>
+        <v>441542</v>
       </c>
       <c r="R18" t="n">
-        <v>7028798</v>
+        <v>7028672</v>
       </c>
       <c r="S18" t="n">
         <v>8</v>
@@ -2736,7 +2766,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2788,10 +2818,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123236259</v>
+        <v>123234252</v>
       </c>
       <c r="B19" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2822,21 +2852,16 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441633</v>
+        <v>441667</v>
       </c>
       <c r="R19" t="n">
-        <v>7028804</v>
+        <v>7028689</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2895,10 +2920,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123235031</v>
+        <v>123233043</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2935,10 +2960,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441542</v>
+        <v>441571</v>
       </c>
       <c r="R20" t="n">
-        <v>7028672</v>
+        <v>7028720</v>
       </c>
       <c r="S20" t="n">
         <v>8</v>
@@ -2971,11 +2996,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3027,10 +3047,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123235737</v>
+        <v>123236460</v>
       </c>
       <c r="B21" t="n">
-        <v>78781</v>
+        <v>97367</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3039,41 +3059,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441617</v>
+        <v>441626</v>
       </c>
       <c r="R21" t="n">
-        <v>7028768</v>
+        <v>7028860</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3113,31 +3138,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123233946</v>
+        <v>123236631</v>
       </c>
       <c r="B4" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,17 +945,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441609</v>
+        <v>441559</v>
       </c>
       <c r="R4" t="n">
-        <v>7028716</v>
+        <v>7028811</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,11 +987,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På gammal gran.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1003,7 +998,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1044,7 +1039,7 @@
         <v>123234752</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1173,10 +1168,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123233597</v>
+        <v>123233772</v>
       </c>
       <c r="B6" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,19 +1202,24 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441569</v>
+        <v>441598</v>
       </c>
       <c r="R6" t="n">
-        <v>7028701</v>
+        <v>7028738</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1249,6 +1249,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1300,10 +1305,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123235689</v>
+        <v>123234048</v>
       </c>
       <c r="B7" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,13 +1345,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441596</v>
+        <v>441630</v>
       </c>
       <c r="R7" t="n">
-        <v>7028775</v>
+        <v>7028692</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1376,6 +1381,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1427,10 +1437,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123235545</v>
+        <v>123235689</v>
       </c>
       <c r="B8" t="n">
-        <v>97373</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1439,46 +1449,41 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441587</v>
+        <v>441596</v>
       </c>
       <c r="R8" t="n">
-        <v>7028776</v>
+        <v>7028775</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1522,6 +1527,26 @@
       <c r="AH8" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,10 +1564,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123236631</v>
+        <v>123233568</v>
       </c>
       <c r="B9" t="n">
-        <v>78786</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,37 +1580,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441559</v>
+        <v>441564</v>
       </c>
       <c r="R9" t="n">
-        <v>7028811</v>
+        <v>7028721</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1617,6 +1656,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1628,27 +1672,7 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1666,10 +1690,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123236343</v>
+        <v>123236259</v>
       </c>
       <c r="B10" t="n">
-        <v>78786</v>
+        <v>97369</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1678,38 +1702,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441640</v>
+        <v>441633</v>
       </c>
       <c r="R10" t="n">
-        <v>7028845</v>
+        <v>7028804</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1752,31 +1781,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1793,10 +1797,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123235737</v>
+        <v>123233946</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1833,13 +1837,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441617</v>
+        <v>441609</v>
       </c>
       <c r="R11" t="n">
-        <v>7028768</v>
+        <v>7028716</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1869,6 +1873,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1920,10 +1929,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123233568</v>
+        <v>123236343</v>
       </c>
       <c r="B12" t="n">
-        <v>57643</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1936,51 +1945,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441564</v>
+        <v>441640</v>
       </c>
       <c r="R12" t="n">
-        <v>7028721</v>
+        <v>7028845</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2012,11 +2007,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2029,6 +2019,26 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2046,10 +2056,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123233772</v>
+        <v>123236127</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2080,21 +2090,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441598</v>
+        <v>441667</v>
       </c>
       <c r="R13" t="n">
-        <v>7028738</v>
+        <v>7028798</v>
       </c>
       <c r="S13" t="n">
         <v>8</v>
@@ -2131,7 +2136,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,10 +2188,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123235901</v>
+        <v>123235545</v>
       </c>
       <c r="B14" t="n">
-        <v>78786</v>
+        <v>97375</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2195,41 +2200,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441683</v>
+        <v>441587</v>
       </c>
       <c r="R14" t="n">
-        <v>7028765</v>
+        <v>7028776</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2261,11 +2271,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2278,26 +2283,6 @@
       <c r="AH14" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2315,10 +2300,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123234048</v>
+        <v>123234252</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>97369</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2327,25 +2312,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2355,13 +2340,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441630</v>
+        <v>441667</v>
       </c>
       <c r="R15" t="n">
-        <v>7028692</v>
+        <v>7028689</v>
       </c>
       <c r="S15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2393,11 +2378,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2406,31 +2386,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2447,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236127</v>
+        <v>123233043</v>
       </c>
       <c r="B16" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2487,10 +2442,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441667</v>
+        <v>441571</v>
       </c>
       <c r="R16" t="n">
-        <v>7028798</v>
+        <v>7028720</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2523,11 +2478,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2579,10 +2529,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123236259</v>
+        <v>123235737</v>
       </c>
       <c r="B17" t="n">
-        <v>97367</v>
+        <v>78788</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2591,46 +2541,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441633</v>
+        <v>441617</v>
       </c>
       <c r="R17" t="n">
-        <v>7028804</v>
+        <v>7028768</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2670,6 +2615,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2686,10 +2656,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123235031</v>
+        <v>123236460</v>
       </c>
       <c r="B18" t="n">
-        <v>78786</v>
+        <v>97369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2698,41 +2668,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441542</v>
+        <v>441626</v>
       </c>
       <c r="R18" t="n">
-        <v>7028672</v>
+        <v>7028860</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2764,11 +2739,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2777,31 +2747,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2818,10 +2763,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123234252</v>
+        <v>123235031</v>
       </c>
       <c r="B19" t="n">
-        <v>97367</v>
+        <v>78788</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2830,25 +2775,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2858,10 +2803,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441667</v>
+        <v>441542</v>
       </c>
       <c r="R19" t="n">
-        <v>7028689</v>
+        <v>7028672</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2896,6 +2841,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2904,6 +2854,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2920,10 +2895,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123233043</v>
+        <v>123233597</v>
       </c>
       <c r="B20" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2960,13 +2935,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441571</v>
+        <v>441569</v>
       </c>
       <c r="R20" t="n">
-        <v>7028720</v>
+        <v>7028701</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3047,10 +3022,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123236460</v>
+        <v>123235901</v>
       </c>
       <c r="B21" t="n">
-        <v>97367</v>
+        <v>78788</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3059,46 +3034,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441626</v>
+        <v>441683</v>
       </c>
       <c r="R21" t="n">
-        <v>7028860</v>
+        <v>7028765</v>
       </c>
       <c r="S21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3130,6 +3100,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på en gammal gran.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3138,6 +3113,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -2402,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123233043</v>
+        <v>123236460</v>
       </c>
       <c r="B16" t="n">
-        <v>78788</v>
+        <v>97369</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2414,41 +2414,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441571</v>
+        <v>441626</v>
       </c>
       <c r="R16" t="n">
-        <v>7028720</v>
+        <v>7028860</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2488,31 +2493,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2529,7 +2509,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235737</v>
+        <v>123233043</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2569,13 +2549,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441617</v>
+        <v>441571</v>
       </c>
       <c r="R17" t="n">
-        <v>7028768</v>
+        <v>7028720</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2656,10 +2636,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123236460</v>
+        <v>123235737</v>
       </c>
       <c r="B18" t="n">
-        <v>97369</v>
+        <v>78788</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2668,46 +2648,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441626</v>
+        <v>441617</v>
       </c>
       <c r="R18" t="n">
-        <v>7028860</v>
+        <v>7028768</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2747,6 +2722,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -2402,10 +2402,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123236460</v>
+        <v>123233043</v>
       </c>
       <c r="B16" t="n">
-        <v>97369</v>
+        <v>78788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2414,46 +2414,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441626</v>
+        <v>441571</v>
       </c>
       <c r="R16" t="n">
-        <v>7028860</v>
+        <v>7028720</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2493,6 +2488,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2509,7 +2529,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123233043</v>
+        <v>123235737</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2549,13 +2569,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441571</v>
+        <v>441617</v>
       </c>
       <c r="R17" t="n">
-        <v>7028720</v>
+        <v>7028768</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2636,10 +2656,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123235737</v>
+        <v>123236460</v>
       </c>
       <c r="B18" t="n">
-        <v>78788</v>
+        <v>97369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2648,41 +2668,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441617</v>
+        <v>441626</v>
       </c>
       <c r="R18" t="n">
-        <v>7028768</v>
+        <v>7028860</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2722,31 +2747,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">

--- a/artfynd/A 5681-2025 artfynd.xlsx
+++ b/artfynd/A 5681-2025 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123236631</v>
+        <v>123233568</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +925,51 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>441559</v>
+        <v>441564</v>
       </c>
       <c r="R4" t="n">
-        <v>7028811</v>
+        <v>7028721</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,6 +1001,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -998,27 +1017,7 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1036,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123234752</v>
+        <v>123236460</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,38 +1047,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>441583</v>
+        <v>441626</v>
       </c>
       <c r="R5" t="n">
-        <v>7028658</v>
+        <v>7028860</v>
       </c>
       <c r="S5" t="n">
         <v>9</v>
@@ -1114,11 +1118,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en gammal gran intill ett fuktstråk.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1127,31 +1126,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1168,7 +1142,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123233772</v>
+        <v>123235901</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1202,24 +1176,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>441598</v>
+        <v>441683</v>
       </c>
       <c r="R6" t="n">
-        <v>7028738</v>
+        <v>7028765</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1253,7 +1222,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
+          <t>Långväxta bålar på en gammal gran.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1305,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123234048</v>
+        <v>123235545</v>
       </c>
       <c r="B7" t="n">
-        <v>78788</v>
+        <v>96963</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1317,41 +1286,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>441630</v>
+        <v>441587</v>
       </c>
       <c r="R7" t="n">
-        <v>7028692</v>
+        <v>7028776</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1383,11 +1357,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1400,26 +1369,6 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1437,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123235689</v>
+        <v>123234252</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1449,25 +1398,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1477,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>441596</v>
+        <v>441667</v>
       </c>
       <c r="R8" t="n">
-        <v>7028775</v>
+        <v>7028689</v>
       </c>
       <c r="S8" t="n">
         <v>8</v>
@@ -1523,31 +1472,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1564,10 +1488,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123233568</v>
+        <v>123234048</v>
       </c>
       <c r="B9" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1580,51 +1504,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>441564</v>
+        <v>441630</v>
       </c>
       <c r="R9" t="n">
-        <v>7028721</v>
+        <v>7028692</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1658,7 +1568,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Fyndplatsen finns i gammal flerskiktad granskog.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1673,6 +1583,26 @@
       <c r="AH9" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1690,10 +1620,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123236259</v>
+        <v>123236127</v>
       </c>
       <c r="B10" t="n">
-        <v>97369</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1702,43 +1632,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>441633</v>
+        <v>441667</v>
       </c>
       <c r="R10" t="n">
-        <v>7028804</v>
+        <v>7028798</v>
       </c>
       <c r="S10" t="n">
         <v>8</v>
@@ -1773,6 +1698,11 @@
           <t>2025-03-15</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1781,6 +1711,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1797,7 +1752,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123233946</v>
+        <v>123234752</v>
       </c>
       <c r="B11" t="n">
         <v>78788</v>
@@ -1837,13 +1792,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>441609</v>
+        <v>441583</v>
       </c>
       <c r="R11" t="n">
-        <v>7028716</v>
+        <v>7028658</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1877,7 +1832,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>På en gammal gran intill ett fuktstråk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1929,7 +1884,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123236343</v>
+        <v>123235737</v>
       </c>
       <c r="B12" t="n">
         <v>78788</v>
@@ -1965,17 +1920,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>441640</v>
+        <v>441617</v>
       </c>
       <c r="R12" t="n">
-        <v>7028845</v>
+        <v>7028768</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2033,12 +1988,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2056,7 +2011,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123236127</v>
+        <v>123233597</v>
       </c>
       <c r="B13" t="n">
         <v>78788</v>
@@ -2096,13 +2051,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>441667</v>
+        <v>441569</v>
       </c>
       <c r="R13" t="n">
-        <v>7028798</v>
+        <v>7028701</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2132,11 +2087,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-15</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2188,10 +2138,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123235545</v>
+        <v>123236631</v>
       </c>
       <c r="B14" t="n">
-        <v>97375</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2200,46 +2150,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>441587</v>
+        <v>441559</v>
       </c>
       <c r="R14" t="n">
-        <v>7028776</v>
+        <v>7028811</v>
       </c>
       <c r="S14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2282,7 +2227,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2300,10 +2265,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123234252</v>
+        <v>123235689</v>
       </c>
       <c r="B15" t="n">
-        <v>97369</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2312,25 +2277,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2340,10 +2305,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>441667</v>
+        <v>441596</v>
       </c>
       <c r="R15" t="n">
-        <v>7028689</v>
+        <v>7028775</v>
       </c>
       <c r="S15" t="n">
         <v>8</v>
@@ -2386,6 +2351,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2402,7 +2392,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123233043</v>
+        <v>123235031</v>
       </c>
       <c r="B16" t="n">
         <v>78788</v>
@@ -2442,10 +2432,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>441571</v>
+        <v>441542</v>
       </c>
       <c r="R16" t="n">
-        <v>7028720</v>
+        <v>7028672</v>
       </c>
       <c r="S16" t="n">
         <v>8</v>
@@ -2478,6 +2468,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2529,7 +2524,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123235737</v>
+        <v>123233043</v>
       </c>
       <c r="B17" t="n">
         <v>78788</v>
@@ -2569,13 +2564,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>441617</v>
+        <v>441571</v>
       </c>
       <c r="R17" t="n">
-        <v>7028768</v>
+        <v>7028720</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2656,10 +2651,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123236460</v>
+        <v>123236259</v>
       </c>
       <c r="B18" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2697,17 +2692,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmon, Hästmon, Jmt</t>
+          <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>441626</v>
+        <v>441633</v>
       </c>
       <c r="R18" t="n">
-        <v>7028860</v>
+        <v>7028804</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2763,7 +2758,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123235031</v>
+        <v>123233772</v>
       </c>
       <c r="B19" t="n">
         <v>78788</v>
@@ -2797,16 +2792,21 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Raskhus, Raskhus, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>441542</v>
+        <v>441598</v>
       </c>
       <c r="R19" t="n">
-        <v>7028672</v>
+        <v>7028738</v>
       </c>
       <c r="S19" t="n">
         <v>8</v>
@@ -2843,7 +2843,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Enstaka bålar.</t>
+          <t>Långväxta bålar på gammal gran. Vissa bålar är fertila med apothecier.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2895,7 +2895,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123233597</v>
+        <v>123233946</v>
       </c>
       <c r="B20" t="n">
         <v>78788</v>
@@ -2935,13 +2935,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>441569</v>
+        <v>441609</v>
       </c>
       <c r="R20" t="n">
-        <v>7028701</v>
+        <v>7028716</v>
       </c>
       <c r="S20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2971,6 +2971,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-15</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3022,7 +3027,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123235901</v>
+        <v>123236343</v>
       </c>
       <c r="B21" t="n">
         <v>78788</v>
@@ -3058,17 +3063,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Raskhus, Raskhus, Jmt</t>
+          <t>Hästmon, Hästmon, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>441683</v>
+        <v>441640</v>
       </c>
       <c r="R21" t="n">
-        <v>7028765</v>
+        <v>7028845</v>
       </c>
       <c r="S21" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3100,11 +3105,6 @@
           <t>2025-03-15</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på en gammal gran.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
